--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3190" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3190" uniqueCount="440">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T11:09:51+00:00</t>
+    <t>2022-10-04T14:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -481,7 +481,7 @@
 </t>
   </si>
   <si>
-    <t>ConditionLastAssertedDate</t>
+    <t>Last date a condition was confirmed valid in its current state</t>
   </si>
   <si>
     <t>Extension for the last date a condition was confirmed valid with its current clinical- and verification status, stage and severity, typically the last performed follow-up</t>
@@ -494,7 +494,7 @@
 </t>
   </si>
   <si>
-    <t>NotFollowedAnymore</t>
+    <t>Date where a condition lost focus in a specific clinical context</t>
   </si>
   <si>
     <t>Extension for the date where a condition lost focus in a specific clinical context</t>
@@ -785,7 +785,7 @@
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
+    <t>Condition code, [DA] tilstandskode</t>
   </si>
   <si>
     <t>A reference to a code defined by a terminology system.</t>
@@ -816,6 +816,9 @@
     <t>FSIIIConditionCode</t>
   </si>
   <si>
+    <t>[DA] FSIII tilstandskode</t>
+  </si>
+  <si>
     <t>Condition.code.coding.id</t>
   </si>
   <si>
@@ -943,10 +946,16 @@
     <t>SCTConditionCode</t>
   </si>
   <si>
+    <t>SNOMED CT condition code</t>
+  </si>
+  <si>
     <t>http://snomed.info/sct</t>
   </si>
   <si>
-    <t>FFBCodes</t>
+    <t>FFBConditionCode</t>
+  </si>
+  <si>
+    <t>[DA] FFB undertemakode</t>
   </si>
   <si>
     <t>urn:oid:1.2.208.176.2.22</t>
@@ -955,10 +964,16 @@
     <t>SKS-D</t>
   </si>
   <si>
+    <t>[DA] Kode fra D-hierarkiet i SKS</t>
+  </si>
+  <si>
     <t>urn:oid:1.2.208.176.2.4.12</t>
   </si>
   <si>
-    <t>ICPC2codes</t>
+    <t>ICPC2code</t>
+  </si>
+  <si>
+    <t>ICPC2 code</t>
   </si>
   <si>
     <t>urn:oid:1.2.208.176.2.31</t>
@@ -4333,7 +4348,7 @@
         <v>243</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>245</v>
@@ -4426,7 +4441,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4541,7 +4556,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4658,7 +4673,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4684,16 +4699,16 @@
         <v>103</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O26" t="s" s="2">
         <v>78</v>
@@ -4703,7 +4718,7 @@
         <v>78</v>
       </c>
       <c r="R26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>78</v>
@@ -4742,7 +4757,7 @@
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>79</v>
@@ -4763,10 +4778,10 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -4777,7 +4792,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4803,13 +4818,13 @@
         <v>232</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
@@ -4859,7 +4874,7 @@
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>79</v>
@@ -4880,10 +4895,10 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4894,7 +4909,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4920,14 +4935,14 @@
         <v>109</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>78</v>
@@ -4976,7 +4991,7 @@
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>79</v>
@@ -4997,10 +5012,10 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5011,7 +5026,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5037,14 +5052,14 @@
         <v>232</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
@@ -5093,7 +5108,7 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>79</v>
@@ -5114,10 +5129,10 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5128,7 +5143,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5151,19 +5166,19 @@
         <v>90</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O30" t="s" s="2">
         <v>78</v>
@@ -5212,7 +5227,7 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>79</v>
@@ -5233,10 +5248,10 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5250,7 +5265,7 @@
         <v>242</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>78</v>
@@ -5275,7 +5290,7 @@
         <v>243</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>244</v>
+        <v>297</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>245</v>
@@ -5366,7 +5381,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -5481,7 +5496,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5598,7 +5613,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5624,16 +5639,16 @@
         <v>103</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>78</v>
@@ -5643,7 +5658,7 @@
         <v>78</v>
       </c>
       <c r="R34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>78</v>
@@ -5682,7 +5697,7 @@
         <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>79</v>
@@ -5703,10 +5718,10 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5717,7 +5732,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5743,13 +5758,13 @@
         <v>232</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
@@ -5799,7 +5814,7 @@
         <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>79</v>
@@ -5820,10 +5835,10 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5834,7 +5849,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5860,14 +5875,14 @@
         <v>109</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>78</v>
@@ -5916,7 +5931,7 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>79</v>
@@ -5937,10 +5952,10 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5951,7 +5966,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5977,14 +5992,14 @@
         <v>232</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>78</v>
@@ -6033,7 +6048,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>79</v>
@@ -6054,10 +6069,10 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6068,7 +6083,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6091,19 +6106,19 @@
         <v>90</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6152,7 +6167,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>79</v>
@@ -6173,10 +6188,10 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6190,7 +6205,7 @@
         <v>242</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>78</v>
@@ -6215,7 +6230,7 @@
         <v>243</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>245</v>
@@ -6308,7 +6323,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6423,7 +6438,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6540,7 +6555,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6566,16 +6581,16 @@
         <v>103</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O42" t="s" s="2">
         <v>78</v>
@@ -6585,7 +6600,7 @@
         <v>78</v>
       </c>
       <c r="R42" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>78</v>
@@ -6624,7 +6639,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>79</v>
@@ -6645,10 +6660,10 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6659,7 +6674,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6685,13 +6700,13 @@
         <v>232</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
@@ -6741,7 +6756,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>79</v>
@@ -6762,10 +6777,10 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6776,7 +6791,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6802,14 +6817,14 @@
         <v>109</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>78</v>
@@ -6858,7 +6873,7 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>79</v>
@@ -6879,10 +6894,10 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -6893,7 +6908,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6919,14 +6934,14 @@
         <v>232</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>78</v>
@@ -6975,7 +6990,7 @@
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>79</v>
@@ -6996,10 +7011,10 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7010,7 +7025,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7033,19 +7048,19 @@
         <v>90</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O46" t="s" s="2">
         <v>78</v>
@@ -7094,7 +7109,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>79</v>
@@ -7115,10 +7130,10 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7132,7 +7147,7 @@
         <v>242</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>78</v>
@@ -7157,7 +7172,7 @@
         <v>243</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>245</v>
@@ -7250,7 +7265,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7365,7 +7380,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7482,7 +7497,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -7508,16 +7523,16 @@
         <v>103</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>78</v>
@@ -7527,7 +7542,7 @@
         <v>78</v>
       </c>
       <c r="R50" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>78</v>
@@ -7566,7 +7581,7 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>79</v>
@@ -7587,10 +7602,10 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7601,7 +7616,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7627,13 +7642,13 @@
         <v>232</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -7683,7 +7698,7 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>79</v>
@@ -7704,10 +7719,10 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7718,7 +7733,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7744,14 +7759,14 @@
         <v>109</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>78</v>
@@ -7800,7 +7815,7 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>79</v>
@@ -7821,10 +7836,10 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -7835,7 +7850,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -7861,14 +7876,14 @@
         <v>232</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>78</v>
@@ -7917,7 +7932,7 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>79</v>
@@ -7938,10 +7953,10 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -7952,7 +7967,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -7975,19 +7990,19 @@
         <v>90</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>78</v>
@@ -8036,7 +8051,7 @@
         <v>78</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>79</v>
@@ -8057,10 +8072,10 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8074,7 +8089,7 @@
         <v>242</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>78</v>
@@ -8099,7 +8114,7 @@
         <v>243</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>244</v>
+        <v>306</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>245</v>
@@ -8192,7 +8207,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8307,7 +8322,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8424,7 +8439,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8450,16 +8465,16 @@
         <v>103</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>78</v>
@@ -8469,7 +8484,7 @@
         <v>78</v>
       </c>
       <c r="R58" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>78</v>
@@ -8508,7 +8523,7 @@
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>79</v>
@@ -8529,10 +8544,10 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8543,7 +8558,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8569,13 +8584,13 @@
         <v>232</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
@@ -8625,7 +8640,7 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>79</v>
@@ -8646,10 +8661,10 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8660,7 +8675,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8686,14 +8701,14 @@
         <v>109</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>78</v>
@@ -8742,7 +8757,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>79</v>
@@ -8763,10 +8778,10 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8777,7 +8792,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -8803,14 +8818,14 @@
         <v>232</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -8859,7 +8874,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>79</v>
@@ -8880,10 +8895,10 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -8894,7 +8909,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -8917,19 +8932,19 @@
         <v>90</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -8978,7 +8993,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>79</v>
@@ -8999,10 +9014,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9013,7 +9028,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9039,16 +9054,16 @@
         <v>232</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9097,7 +9112,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>79</v>
@@ -9118,10 +9133,10 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9132,7 +9147,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9158,13 +9173,13 @@
         <v>173</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
@@ -9193,28 +9208,28 @@
         <v>222</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE64" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>79</v>
@@ -9232,28 +9247,28 @@
         <v>78</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9272,17 +9287,17 @@
         <v>90</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>78</v>
@@ -9331,7 +9346,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>89</v>
@@ -9346,19 +9361,19 @@
         <v>101</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -9366,7 +9381,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9389,16 +9404,16 @@
         <v>90</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
@@ -9448,7 +9463,7 @@
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>79</v>
@@ -9463,19 +9478,19 @@
         <v>101</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9483,7 +9498,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9506,16 +9521,16 @@
         <v>90</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
@@ -9565,7 +9580,7 @@
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>79</v>
@@ -9580,19 +9595,19 @@
         <v>101</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -9600,7 +9615,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9623,16 +9638,16 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
@@ -9682,7 +9697,7 @@
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>79</v>
@@ -9691,7 +9706,7 @@
         <v>89</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>101</v>
@@ -9706,10 +9721,10 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9717,7 +9732,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9740,13 +9755,13 @@
         <v>90</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -9797,7 +9812,7 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>79</v>
@@ -9818,13 +9833,13 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9832,7 +9847,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -9855,13 +9870,13 @@
         <v>90</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -9912,7 +9927,7 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>79</v>
@@ -9936,10 +9951,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -9947,7 +9962,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -9970,13 +9985,13 @@
         <v>90</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -10027,7 +10042,7 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>79</v>
@@ -10048,13 +10063,13 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10062,7 +10077,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10085,13 +10100,13 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -10142,7 +10157,7 @@
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>79</v>
@@ -10154,7 +10169,7 @@
         <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>78</v>
@@ -10166,7 +10181,7 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10177,7 +10192,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10292,7 +10307,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10409,11 +10424,11 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10435,10 +10450,10 @@
         <v>134</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>160</v>
@@ -10493,7 +10508,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>79</v>
@@ -10528,7 +10543,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
@@ -10554,10 +10569,10 @@
         <v>173</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -10587,10 +10602,10 @@
         <v>222</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>78</v>
@@ -10608,7 +10623,7 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>79</v>
@@ -10617,7 +10632,7 @@
         <v>89</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>101</v>
@@ -10626,7 +10641,7 @@
         <v>78</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>183</v>
@@ -10643,7 +10658,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -10666,13 +10681,13 @@
         <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -10723,7 +10738,7 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>79</v>
@@ -10732,7 +10747,7 @@
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>101</v>
@@ -10747,7 +10762,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10758,7 +10773,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
@@ -10784,10 +10799,10 @@
         <v>173</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -10817,10 +10832,10 @@
         <v>222</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Z78" t="s" s="2">
         <v>78</v>
@@ -10838,7 +10853,7 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>79</v>
@@ -10862,7 +10877,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -10873,7 +10888,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
@@ -10896,16 +10911,16 @@
         <v>78</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
@@ -10955,7 +10970,7 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>79</v>
@@ -10967,7 +10982,7 @@
         <v>78</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>78</v>
@@ -10979,7 +10994,7 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -10990,7 +11005,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
@@ -11105,7 +11120,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -11222,11 +11237,11 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11248,10 +11263,10 @@
         <v>134</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="M82" t="s" s="2">
         <v>160</v>
@@ -11306,7 +11321,7 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>79</v>
@@ -11341,7 +11356,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
@@ -11367,10 +11382,10 @@
         <v>173</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -11400,10 +11415,10 @@
         <v>222</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="Z83" t="s" s="2">
         <v>78</v>
@@ -11421,7 +11436,7 @@
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>79</v>
@@ -11430,13 +11445,13 @@
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>203</v>
@@ -11445,10 +11460,10 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>78</v>
@@ -11456,7 +11471,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
@@ -11479,13 +11494,13 @@
         <v>90</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
@@ -11536,7 +11551,7 @@
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>79</v>
@@ -11545,7 +11560,7 @@
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>101</v>
@@ -11560,10 +11575,10 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
@@ -11571,7 +11586,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
@@ -11594,13 +11609,13 @@
         <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -11651,7 +11666,7 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>79</v>
@@ -11666,16 +11681,16 @@
         <v>101</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T14:18:04+00:00</t>
+    <t>2022-10-04T19:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T19:52:49+00:00</t>
+    <t>2022-10-04T20:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3190" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3190" uniqueCount="439">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T20:54:27+00:00</t>
+    <t>2022-10-11T09:25:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -262,10 +262,6 @@
   </si>
   <si>
     <t>A clinical condition, problem, diagnosis, or other event, situation, issue, or clinical concept that has risen to a level of concern.</t>
-  </si>
-  <si>
-    <t>con-3:Condition.clinicalStatus SHALL be present if verificationStatus is not entered-in-error and category is problem-list-item {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
-con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1957,19 +1953,19 @@
         <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AJ2" t="s" s="2">
+      <c r="AK2" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AK2" t="s" s="2">
+      <c r="AL2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AM2" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>78</v>
@@ -1980,7 +1976,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -1991,28 +1987,28 @@
         <v>79</v>
       </c>
       <c r="F3" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G3" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I3" t="s" s="2">
+      <c r="J3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" t="s" s="2">
@@ -2062,13 +2058,13 @@
         <v>78</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>78</v>
@@ -2097,7 +2093,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -2108,25 +2104,25 @@
         <v>79</v>
       </c>
       <c r="F4" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I4" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J4" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K4" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="K4" t="s" s="2">
+      <c r="L4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="L4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -2177,19 +2173,19 @@
         <v>78</v>
       </c>
       <c r="AE4" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AF4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI4" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>78</v>
@@ -2212,7 +2208,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -2223,28 +2219,28 @@
         <v>79</v>
       </c>
       <c r="F5" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H5" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="K5" t="s" s="2">
+      <c r="L5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" t="s" s="2">
@@ -2294,19 +2290,19 @@
         <v>78</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>78</v>
@@ -2329,7 +2325,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -2340,7 +2336,7 @@
         <v>79</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>78</v>
@@ -2352,16 +2348,16 @@
         <v>78</v>
       </c>
       <c r="J6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" t="s" s="2">
@@ -2387,43 +2383,43 @@
         <v>78</v>
       </c>
       <c r="W6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="X6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="X6" t="s" s="2">
+      <c r="Y6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Z6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="AF6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>78</v>
@@ -2446,18 +2442,18 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>78</v>
@@ -2469,16 +2465,16 @@
         <v>78</v>
       </c>
       <c r="J7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="K7" t="s" s="2">
+      <c r="L7" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" t="s" s="2">
@@ -2528,31 +2524,31 @@
         <v>78</v>
       </c>
       <c r="AE7" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>78</v>
@@ -2563,11 +2559,11 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
@@ -2586,16 +2582,16 @@
         <v>78</v>
       </c>
       <c r="J8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="K8" t="s" s="2">
+      <c r="L8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" t="s" s="2">
@@ -2645,7 +2641,7 @@
         <v>78</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AF8" t="s" s="2">
         <v>79</v>
@@ -2669,7 +2665,7 @@
         <v>78</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>78</v>
@@ -2680,7 +2676,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -2703,13 +2699,13 @@
         <v>78</v>
       </c>
       <c r="J9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="K9" t="s" s="2">
+      <c r="L9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -2748,17 +2744,17 @@
         <v>78</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AB9" s="2"/>
       <c r="AC9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AE9" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>79</v>
@@ -2770,7 +2766,7 @@
         <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>78</v>
@@ -2793,10 +2789,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>78</v>
@@ -2806,7 +2802,7 @@
         <v>79</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>78</v>
@@ -2818,16 +2814,16 @@
         <v>78</v>
       </c>
       <c r="J10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="K10" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="K10" t="s" s="2">
+      <c r="L10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" t="s" s="2">
@@ -2877,7 +2873,7 @@
         <v>78</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AF10" t="s" s="2">
         <v>79</v>
@@ -2886,22 +2882,22 @@
         <v>80</v>
       </c>
       <c r="AH10" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM10" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="AI10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AJ10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>78</v>
@@ -2912,10 +2908,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>78</v>
@@ -2925,7 +2921,7 @@
         <v>79</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>78</v>
@@ -2937,13 +2933,13 @@
         <v>78</v>
       </c>
       <c r="J11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="K11" t="s" s="2">
+      <c r="L11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -2994,7 +2990,7 @@
         <v>78</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>79</v>
@@ -3003,10 +2999,10 @@
         <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>78</v>
@@ -3029,10 +3025,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>78</v>
@@ -3042,7 +3038,7 @@
         <v>79</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>78</v>
@@ -3054,13 +3050,13 @@
         <v>78</v>
       </c>
       <c r="J12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="K12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="K12" t="s" s="2">
+      <c r="L12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -3111,7 +3107,7 @@
         <v>78</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>79</v>
@@ -3120,10 +3116,10 @@
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>78</v>
@@ -3146,11 +3142,11 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
@@ -3163,25 +3159,25 @@
         <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O13" t="s" s="2">
         <v>78</v>
@@ -3230,7 +3226,7 @@
         <v>78</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>79</v>
@@ -3242,7 +3238,7 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>78</v>
@@ -3254,7 +3250,7 @@
         <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>78</v>
@@ -3265,7 +3261,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -3285,22 +3281,22 @@
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="K14" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="K14" t="s" s="2">
+      <c r="L14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="O14" t="s" s="2">
         <v>78</v>
@@ -3349,7 +3345,7 @@
         <v>78</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>79</v>
@@ -3361,22 +3357,22 @@
         <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AK14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>78</v>
@@ -3384,7 +3380,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -3395,28 +3391,28 @@
         <v>79</v>
       </c>
       <c r="F15" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="I15" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="K15" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="K15" t="s" s="2">
+      <c r="L15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
@@ -3442,58 +3438,58 @@
         <v>78</v>
       </c>
       <c r="W15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="X15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="X15" t="s" s="2">
+      <c r="Y15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH15" t="s" s="2">
+      <c r="AI15" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AI15" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
+      <c r="AK15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>78</v>
@@ -3501,7 +3497,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3512,28 +3508,28 @@
         <v>79</v>
       </c>
       <c r="F16" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="I16" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
@@ -3559,66 +3555,66 @@
         <v>78</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH16" t="s" s="2">
+      <c r="AI16" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AK16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AI16" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AL16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>196</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3641,16 +3637,16 @@
         <v>78</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
@@ -3676,14 +3672,14 @@
         <v>78</v>
       </c>
       <c r="W17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="X17" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>202</v>
-      </c>
       <c r="Z17" t="s" s="2">
         <v>78</v>
       </c>
@@ -3700,7 +3696,7 @@
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>79</v>
@@ -3712,22 +3708,22 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>78</v>
@@ -3735,7 +3731,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -3746,7 +3742,7 @@
         <v>79</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>78</v>
@@ -3758,16 +3754,16 @@
         <v>78</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
@@ -3793,99 +3789,99 @@
         <v>78</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK18" t="s" s="2">
+      <c r="AL18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F19" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I19" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J19" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O19" t="s" s="2">
         <v>78</v>
@@ -3910,66 +3906,66 @@
         <v>78</v>
       </c>
       <c r="W19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="X19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="X19" t="s" s="2">
+      <c r="Y19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="Y19" t="s" s="2">
+      <c r="Z19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Z19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
+      <c r="AK19" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AK19" t="s" s="2">
+      <c r="AL19" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -3980,7 +3976,7 @@
         <v>79</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>78</v>
@@ -3992,13 +3988,13 @@
         <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="K20" t="s" s="2">
+      <c r="L20" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -4049,31 +4045,31 @@
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
@@ -4084,11 +4080,11 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -4107,16 +4103,16 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="M21" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -4154,19 +4150,19 @@
         <v>78</v>
       </c>
       <c r="AA21" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD21" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AB21" t="s" s="2">
+      <c r="AE21" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>79</v>
@@ -4178,7 +4174,7 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>78</v>
@@ -4190,7 +4186,7 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4201,7 +4197,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4221,22 +4217,22 @@
         <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="K22" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="K22" t="s" s="2">
+      <c r="L22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O22" t="s" s="2">
         <v>78</v>
@@ -4273,19 +4269,19 @@
         <v>78</v>
       </c>
       <c r="AA22" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AB22" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AB22" t="s" s="2">
+      <c r="AC22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AE22" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>79</v>
@@ -4297,7 +4293,7 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>78</v>
@@ -4306,10 +4302,10 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4320,10 +4316,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>78</v>
@@ -4333,31 +4329,31 @@
         <v>79</v>
       </c>
       <c r="F23" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I23" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O23" t="s" s="2">
         <v>78</v>
@@ -4406,7 +4402,7 @@
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>79</v>
@@ -4418,7 +4414,7 @@
         <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>78</v>
@@ -4427,10 +4423,10 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -4441,7 +4437,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4452,7 +4448,7 @@
         <v>79</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>78</v>
@@ -4464,13 +4460,13 @@
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="K24" t="s" s="2">
+      <c r="L24" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -4521,31 +4517,31 @@
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4556,11 +4552,11 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -4579,16 +4575,16 @@
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="M25" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
@@ -4626,19 +4622,19 @@
         <v>78</v>
       </c>
       <c r="AA25" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD25" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AB25" t="s" s="2">
+      <c r="AE25" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>79</v>
@@ -4650,7 +4646,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>78</v>
@@ -4662,7 +4658,7 @@
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4673,7 +4669,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4681,34 +4677,34 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I26" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="F26" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J26" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O26" t="s" s="2">
         <v>78</v>
@@ -4718,70 +4714,70 @@
         <v>78</v>
       </c>
       <c r="R26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE26" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="S26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE26" t="s" s="2">
+      <c r="AF26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AF26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -4792,7 +4788,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4803,28 +4799,28 @@
         <v>79</v>
       </c>
       <c r="F27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I27" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J27" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
@@ -4874,31 +4870,31 @@
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AF27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4909,7 +4905,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4920,29 +4916,29 @@
         <v>79</v>
       </c>
       <c r="F28" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I28" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J28" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>78</v>
@@ -4991,31 +4987,31 @@
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AF28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5026,7 +5022,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5037,29 +5033,29 @@
         <v>79</v>
       </c>
       <c r="F29" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I29" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J29" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
@@ -5108,31 +5104,31 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AF29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5143,7 +5139,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5154,31 +5150,31 @@
         <v>79</v>
       </c>
       <c r="F30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I30" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="K30" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="K30" t="s" s="2">
+      <c r="L30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O30" t="s" s="2">
         <v>78</v>
@@ -5227,31 +5223,31 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AF30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5262,10 +5258,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>78</v>
@@ -5275,31 +5271,31 @@
         <v>79</v>
       </c>
       <c r="F31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I31" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J31" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O31" t="s" s="2">
         <v>78</v>
@@ -5324,11 +5320,11 @@
         <v>78</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="X31" s="2"/>
       <c r="Y31" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>78</v>
@@ -5346,7 +5342,7 @@
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>79</v>
@@ -5358,7 +5354,7 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>78</v>
@@ -5367,10 +5363,10 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5381,7 +5377,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -5392,7 +5388,7 @@
         <v>79</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>78</v>
@@ -5404,13 +5400,13 @@
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="K32" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="K32" t="s" s="2">
+      <c r="L32" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -5461,31 +5457,31 @@
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5496,11 +5492,11 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5519,16 +5515,16 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="M33" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
@@ -5566,19 +5562,19 @@
         <v>78</v>
       </c>
       <c r="AA33" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD33" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AB33" t="s" s="2">
+      <c r="AE33" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>79</v>
@@ -5590,7 +5586,7 @@
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>78</v>
@@ -5602,7 +5598,7 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5613,7 +5609,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5621,34 +5617,34 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I34" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="F34" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J34" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>78</v>
@@ -5658,7 +5654,7 @@
         <v>78</v>
       </c>
       <c r="R34" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>78</v>
@@ -5697,31 +5693,31 @@
         <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AF34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5732,7 +5728,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5743,28 +5739,28 @@
         <v>79</v>
       </c>
       <c r="F35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I35" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J35" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
@@ -5814,31 +5810,31 @@
         <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AF35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5849,7 +5845,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5860,29 +5856,29 @@
         <v>79</v>
       </c>
       <c r="F36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I36" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J36" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>78</v>
@@ -5931,31 +5927,31 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AF36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5966,7 +5962,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5977,29 +5973,29 @@
         <v>79</v>
       </c>
       <c r="F37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I37" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J37" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>78</v>
@@ -6048,31 +6044,31 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AF37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6083,7 +6079,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6094,31 +6090,31 @@
         <v>79</v>
       </c>
       <c r="F38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I38" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J38" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="K38" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="K38" t="s" s="2">
+      <c r="L38" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6167,31 +6163,31 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AF38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6202,10 +6198,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>78</v>
@@ -6215,31 +6211,31 @@
         <v>79</v>
       </c>
       <c r="F39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I39" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J39" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6288,7 +6284,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>79</v>
@@ -6300,7 +6296,7 @@
         <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>78</v>
@@ -6309,10 +6305,10 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6323,7 +6319,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6334,7 +6330,7 @@
         <v>79</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>78</v>
@@ -6346,13 +6342,13 @@
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="K40" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="K40" t="s" s="2">
+      <c r="L40" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6403,31 +6399,31 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6438,11 +6434,11 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6461,16 +6457,16 @@
         <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L41" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="M41" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
@@ -6508,19 +6504,19 @@
         <v>78</v>
       </c>
       <c r="AA41" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD41" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AB41" t="s" s="2">
+      <c r="AE41" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>79</v>
@@ -6532,7 +6528,7 @@
         <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>78</v>
@@ -6544,7 +6540,7 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6555,7 +6551,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6563,34 +6559,34 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="F42" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J42" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O42" t="s" s="2">
         <v>78</v>
@@ -6600,7 +6596,7 @@
         <v>78</v>
       </c>
       <c r="R42" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>78</v>
@@ -6639,31 +6635,31 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AF42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6674,7 +6670,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6685,28 +6681,28 @@
         <v>79</v>
       </c>
       <c r="F43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I43" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J43" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
@@ -6756,31 +6752,31 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AF43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6791,7 +6787,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6802,29 +6798,29 @@
         <v>79</v>
       </c>
       <c r="F44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I44" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J44" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>78</v>
@@ -6873,31 +6869,31 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AF44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -6908,7 +6904,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6919,29 +6915,29 @@
         <v>79</v>
       </c>
       <c r="F45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I45" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J45" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>78</v>
@@ -6990,31 +6986,31 @@
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AF45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7025,7 +7021,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7036,31 +7032,31 @@
         <v>79</v>
       </c>
       <c r="F46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I46" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J46" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="K46" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="K46" t="s" s="2">
+      <c r="L46" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O46" t="s" s="2">
         <v>78</v>
@@ -7109,31 +7105,31 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AF46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7144,10 +7140,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>78</v>
@@ -7157,31 +7153,31 @@
         <v>79</v>
       </c>
       <c r="F47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I47" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J47" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>78</v>
@@ -7230,7 +7226,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>79</v>
@@ -7242,7 +7238,7 @@
         <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>78</v>
@@ -7251,10 +7247,10 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7265,7 +7261,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7276,7 +7272,7 @@
         <v>79</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>78</v>
@@ -7288,13 +7284,13 @@
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="K48" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="K48" t="s" s="2">
+      <c r="L48" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7345,31 +7341,31 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7380,11 +7376,11 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7403,16 +7399,16 @@
         <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L49" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="M49" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
@@ -7450,19 +7446,19 @@
         <v>78</v>
       </c>
       <c r="AA49" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AB49" t="s" s="2">
+      <c r="AE49" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>79</v>
@@ -7474,7 +7470,7 @@
         <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>78</v>
@@ -7486,7 +7482,7 @@
         <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7497,7 +7493,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -7505,34 +7501,34 @@
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I50" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="F50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J50" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>78</v>
@@ -7542,7 +7538,7 @@
         <v>78</v>
       </c>
       <c r="R50" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>78</v>
@@ -7581,31 +7577,31 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AF50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7616,7 +7612,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7627,28 +7623,28 @@
         <v>79</v>
       </c>
       <c r="F51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I51" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J51" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -7698,31 +7694,31 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AF51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7733,7 +7729,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7744,29 +7740,29 @@
         <v>79</v>
       </c>
       <c r="F52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I52" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J52" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>78</v>
@@ -7815,31 +7811,31 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AF52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -7850,7 +7846,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -7861,29 +7857,29 @@
         <v>79</v>
       </c>
       <c r="F53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I53" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J53" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>78</v>
@@ -7932,31 +7928,31 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AF53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -7967,7 +7963,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -7978,31 +7974,31 @@
         <v>79</v>
       </c>
       <c r="F54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I54" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J54" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="K54" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="K54" t="s" s="2">
+      <c r="L54" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>78</v>
@@ -8051,31 +8047,31 @@
         <v>78</v>
       </c>
       <c r="AE54" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AF54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8086,10 +8082,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>78</v>
@@ -8099,31 +8095,31 @@
         <v>79</v>
       </c>
       <c r="F55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I55" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J55" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>78</v>
@@ -8172,7 +8168,7 @@
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>79</v>
@@ -8184,7 +8180,7 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>78</v>
@@ -8193,10 +8189,10 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8207,7 +8203,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8218,7 +8214,7 @@
         <v>79</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>78</v>
@@ -8230,13 +8226,13 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="K56" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="K56" t="s" s="2">
+      <c r="L56" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
@@ -8287,31 +8283,31 @@
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8322,11 +8318,11 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8345,16 +8341,16 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L57" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="M57" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
@@ -8392,19 +8388,19 @@
         <v>78</v>
       </c>
       <c r="AA57" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AB57" t="s" s="2">
+      <c r="AE57" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>79</v>
@@ -8416,7 +8412,7 @@
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>78</v>
@@ -8428,7 +8424,7 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8439,7 +8435,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8447,34 +8443,34 @@
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I58" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="F58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J58" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>78</v>
@@ -8484,7 +8480,7 @@
         <v>78</v>
       </c>
       <c r="R58" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>78</v>
@@ -8523,31 +8519,31 @@
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AF58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8558,7 +8554,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8569,28 +8565,28 @@
         <v>79</v>
       </c>
       <c r="F59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I59" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J59" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
@@ -8640,31 +8636,31 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AF59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8675,7 +8671,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8686,29 +8682,29 @@
         <v>79</v>
       </c>
       <c r="F60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I60" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J60" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>78</v>
@@ -8757,31 +8753,31 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AF60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8792,7 +8788,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -8803,29 +8799,29 @@
         <v>79</v>
       </c>
       <c r="F61" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I61" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J61" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -8874,31 +8870,31 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AF61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -8909,7 +8905,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -8920,31 +8916,31 @@
         <v>79</v>
       </c>
       <c r="F62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I62" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J62" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="K62" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="K62" t="s" s="2">
+      <c r="L62" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -8993,31 +8989,31 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AF62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9028,7 +9024,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9039,31 +9035,31 @@
         <v>79</v>
       </c>
       <c r="F63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I63" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J63" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9112,31 +9108,31 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AF63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9147,7 +9143,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9167,19 +9163,19 @@
         <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
@@ -9205,14 +9201,14 @@
         <v>78</v>
       </c>
       <c r="W64" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X64" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="Y64" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="Y64" t="s" s="2">
-        <v>321</v>
-      </c>
       <c r="Z64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9229,7 +9225,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>79</v>
@@ -9241,63 +9237,63 @@
         <v>78</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I65" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="F65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J65" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="K65" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="K65" t="s" s="2">
+      <c r="L65" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>78</v>
@@ -9346,34 +9342,34 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AK65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AM65" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -9381,7 +9377,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9392,28 +9388,28 @@
         <v>79</v>
       </c>
       <c r="F66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I66" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J66" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="K66" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="K66" t="s" s="2">
+      <c r="L66" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
@@ -9463,34 +9459,34 @@
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ66" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AK66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AM66" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9498,7 +9494,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9509,28 +9505,28 @@
         <v>79</v>
       </c>
       <c r="F67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I67" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J67" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="K67" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="K67" t="s" s="2">
+      <c r="L67" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
@@ -9580,34 +9576,34 @@
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AK67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL67" t="s" s="2">
+      <c r="AM67" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -9615,7 +9611,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9626,7 +9622,7 @@
         <v>79</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>78</v>
@@ -9638,16 +9634,16 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
@@ -9697,34 +9693,34 @@
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH68" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AI68" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9732,7 +9728,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9743,25 +9739,25 @@
         <v>79</v>
       </c>
       <c r="F69" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I69" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J69" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="K69" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="K69" t="s" s="2">
+      <c r="L69" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -9812,19 +9808,19 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>78</v>
@@ -9833,13 +9829,13 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9847,7 +9843,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -9858,25 +9854,25 @@
         <v>79</v>
       </c>
       <c r="F70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I70" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J70" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="K70" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="K70" t="s" s="2">
+      <c r="L70" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -9927,19 +9923,19 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>78</v>
@@ -9951,10 +9947,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -9962,7 +9958,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -9973,25 +9969,25 @@
         <v>79</v>
       </c>
       <c r="F71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I71" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J71" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="K71" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="K71" t="s" s="2">
+      <c r="L71" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -10042,19 +10038,19 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>78</v>
@@ -10063,13 +10059,13 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10077,7 +10073,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10100,13 +10096,13 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="K72" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="K72" t="s" s="2">
+      <c r="L72" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -10157,7 +10153,7 @@
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>79</v>
@@ -10169,19 +10165,19 @@
         <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10192,7 +10188,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10203,7 +10199,7 @@
         <v>79</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>78</v>
@@ -10215,13 +10211,13 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="K73" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="K73" t="s" s="2">
+      <c r="L73" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -10272,31 +10268,31 @@
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10307,11 +10303,11 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10330,16 +10326,16 @@
         <v>78</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L74" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="M74" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
@@ -10389,7 +10385,7 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>79</v>
@@ -10401,7 +10397,7 @@
         <v>78</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>78</v>
@@ -10413,7 +10409,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10424,11 +10420,11 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10441,25 +10437,25 @@
         <v>78</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="M75" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>78</v>
@@ -10508,7 +10504,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>79</v>
@@ -10520,7 +10516,7 @@
         <v>78</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>78</v>
@@ -10532,7 +10528,7 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10543,7 +10539,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
@@ -10554,7 +10550,7 @@
         <v>79</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>78</v>
@@ -10566,13 +10562,13 @@
         <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -10599,55 +10595,55 @@
         <v>78</v>
       </c>
       <c r="W76" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X76" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="Y76" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="Y76" t="s" s="2">
+      <c r="Z76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH76" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH76" t="s" s="2">
+      <c r="AI76" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK76" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AI76" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="AL76" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -10658,7 +10654,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -10681,13 +10677,13 @@
         <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="K77" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="K77" t="s" s="2">
+      <c r="L77" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -10738,7 +10734,7 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>79</v>
@@ -10747,10 +10743,10 @@
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>78</v>
@@ -10762,7 +10758,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10773,7 +10769,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
@@ -10784,7 +10780,7 @@
         <v>79</v>
       </c>
       <c r="F78" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>78</v>
@@ -10796,13 +10792,13 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -10829,55 +10825,55 @@
         <v>78</v>
       </c>
       <c r="W78" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X78" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="Y78" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="Y78" t="s" s="2">
+      <c r="Z78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -10888,7 +10884,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
@@ -10911,16 +10907,16 @@
         <v>78</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
@@ -10970,7 +10966,7 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>79</v>
@@ -10982,19 +10978,19 @@
         <v>78</v>
       </c>
       <c r="AI79" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11005,7 +11001,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
@@ -11016,7 +11012,7 @@
         <v>79</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>78</v>
@@ -11028,13 +11024,13 @@
         <v>78</v>
       </c>
       <c r="J80" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="K80" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="K80" t="s" s="2">
+      <c r="L80" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
@@ -11085,31 +11081,31 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11120,11 +11116,11 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -11143,16 +11139,16 @@
         <v>78</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L81" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="M81" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
@@ -11202,7 +11198,7 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>79</v>
@@ -11214,7 +11210,7 @@
         <v>78</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>78</v>
@@ -11226,7 +11222,7 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11237,11 +11233,11 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11254,25 +11250,25 @@
         <v>78</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L82" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="M82" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O82" t="s" s="2">
         <v>78</v>
@@ -11321,7 +11317,7 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>79</v>
@@ -11333,7 +11329,7 @@
         <v>78</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>78</v>
@@ -11345,7 +11341,7 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11356,7 +11352,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
@@ -11376,16 +11372,16 @@
         <v>78</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -11412,14 +11408,14 @@
         <v>78</v>
       </c>
       <c r="W83" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X83" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="Y83" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="Y83" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="Z83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11436,7 +11432,7 @@
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>79</v>
@@ -11445,25 +11441,25 @@
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AI83" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
+      <c r="AK83" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AK83" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>78</v>
@@ -11471,7 +11467,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
@@ -11491,16 +11487,16 @@
         <v>78</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J84" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="K84" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="K84" t="s" s="2">
+      <c r="L84" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
@@ -11551,7 +11547,7 @@
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>79</v>
@@ -11560,10 +11556,10 @@
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>78</v>
@@ -11575,10 +11571,10 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
@@ -11586,7 +11582,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
@@ -11609,13 +11605,13 @@
         <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="K85" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="K85" t="s" s="2">
+      <c r="L85" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -11666,7 +11662,7 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>79</v>
@@ -11678,19 +11674,19 @@
         <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ85" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL85" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AK85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL85" t="s" s="2">
+      <c r="AM85" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-11T09:25:49+00:00</t>
+    <t>2022-10-21T11:28:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -480,7 +480,7 @@
     <t>Last date a condition was confirmed valid in its current state</t>
   </si>
   <si>
-    <t>Extension for the last date a condition was confirmed valid with its current clinical- and verification status, stage and severity, typically the last performed follow-up</t>
+    <t>Extension for the last date a Condition-instance was confirmed valid in its current state. E.g. with its current clinical- and verification status, stage and severity. Typically the last performed follow-up</t>
   </si>
   <si>
     <t>notFollowedAnymore</t>
@@ -1033,7 +1033,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient)
 </t>
   </si>
   <si>
@@ -1161,7 +1161,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1180,7 +1180,7 @@
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole)
 </t>
   </si>
   <si>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:28:25+00:00</t>
+    <t>2022-10-21T11:53:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:53:19+00:00</t>
+    <t>2022-10-24T14:23:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T14:23:47+00:00</t>
+    <t>2022-10-24T22:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T22:55:30+00:00</t>
+    <t>2022-11-07T08:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T08:18:22+00:00</t>
+    <t>2022-11-07T15:10:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T15:10:04+00:00</t>
+    <t>2022-11-08T22:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:20:55+00:00</t>
+    <t>2022-11-08T22:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:23:46+00:00</t>
+    <t>2022-11-30T21:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-30T21:48:52+00:00</t>
+    <t>2022-12-01T00:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T00:22:19+00:00</t>
+    <t>2022-12-01T21:15:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T21:15:09+00:00</t>
+    <t>2022-12-05T08:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:13:32+00:00</t>
+    <t>2022-12-05T08:52:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:52:10+00:00</t>
+    <t>2022-12-05T08:58:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:58:17+00:00</t>
+    <t>2022-12-05T09:15:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-18T12:02:45+00:00</t>
+    <t>2023-04-24T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-24T21:40:58+00:00</t>
+    <t>2023-04-25T17:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Condition</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-condition</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -1651,6 +1654,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1998,7 +2016,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2116,7 +2134,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2236,7 +2254,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -2354,7 +2372,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>103</v>
       </c>
@@ -2474,7 +2492,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>109</v>
       </c>
@@ -2594,7 +2612,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -2714,7 +2732,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -2834,7 +2852,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>134</v>
       </c>
@@ -2950,7 +2968,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
@@ -3072,7 +3090,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3192,7 +3210,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>155</v>
       </c>
@@ -3312,7 +3330,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>160</v>
       </c>
@@ -3434,7 +3452,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>167</v>
       </c>
@@ -3556,7 +3574,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>176</v>
       </c>
@@ -3575,7 +3593,7 @@
         <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>91</v>
@@ -3676,7 +3694,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>190</v>
       </c>
@@ -3695,7 +3713,7 @@
         <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>91</v>
@@ -3796,7 +3814,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>201</v>
       </c>
@@ -3815,7 +3833,7 @@
         <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
@@ -3916,7 +3934,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>211</v>
       </c>
@@ -4036,7 +4054,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>221</v>
       </c>
@@ -4049,13 +4067,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>79</v>
@@ -4156,7 +4174,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>235</v>
       </c>
@@ -4274,7 +4292,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>241</v>
       </c>
@@ -4394,7 +4412,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>246</v>
       </c>
@@ -4516,7 +4534,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>257</v>
       </c>
@@ -4640,7 +4658,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>260</v>
       </c>
@@ -4758,7 +4776,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>262</v>
       </c>
@@ -4878,7 +4896,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>264</v>
       </c>
@@ -5000,7 +5018,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>274</v>
       </c>
@@ -5120,7 +5138,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>282</v>
       </c>
@@ -5240,7 +5258,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>290</v>
       </c>
@@ -5360,7 +5378,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>298</v>
       </c>
@@ -5482,7 +5500,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>308</v>
       </c>
@@ -5604,7 +5622,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>311</v>
       </c>
@@ -5722,7 +5740,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>312</v>
       </c>
@@ -5842,7 +5860,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>313</v>
       </c>
@@ -5964,7 +5982,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>315</v>
       </c>
@@ -6084,7 +6102,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>316</v>
       </c>
@@ -6204,7 +6222,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>317</v>
       </c>
@@ -6324,7 +6342,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>318</v>
       </c>
@@ -6446,7 +6464,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>319</v>
       </c>
@@ -6570,7 +6588,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>322</v>
       </c>
@@ -6688,7 +6706,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>323</v>
       </c>
@@ -6808,7 +6826,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>324</v>
       </c>
@@ -6930,7 +6948,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>326</v>
       </c>
@@ -7050,7 +7068,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>327</v>
       </c>
@@ -7170,7 +7188,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>328</v>
       </c>
@@ -7290,7 +7308,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>329</v>
       </c>
@@ -7412,7 +7430,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>330</v>
       </c>
@@ -7536,7 +7554,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>333</v>
       </c>
@@ -7654,7 +7672,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>334</v>
       </c>
@@ -7774,7 +7792,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>335</v>
       </c>
@@ -7896,7 +7914,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>337</v>
       </c>
@@ -8016,7 +8034,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>338</v>
       </c>
@@ -8136,7 +8154,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>339</v>
       </c>
@@ -8256,7 +8274,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>340</v>
       </c>
@@ -8378,7 +8396,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>341</v>
       </c>
@@ -8502,7 +8520,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>344</v>
       </c>
@@ -8620,7 +8638,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>345</v>
       </c>
@@ -8740,7 +8758,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>346</v>
       </c>
@@ -8862,7 +8880,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>348</v>
       </c>
@@ -8982,7 +9000,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>349</v>
       </c>
@@ -9102,7 +9120,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>350</v>
       </c>
@@ -9222,7 +9240,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>351</v>
       </c>
@@ -9344,7 +9362,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>352</v>
       </c>
@@ -9466,7 +9484,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>360</v>
       </c>
@@ -9586,7 +9604,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>369</v>
       </c>
@@ -9605,7 +9623,7 @@
         <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>79</v>
@@ -9706,7 +9724,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>379</v>
       </c>
@@ -9826,7 +9844,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>388</v>
       </c>
@@ -9946,7 +9964,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>397</v>
       </c>
@@ -10066,7 +10084,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>404</v>
       </c>
@@ -10184,7 +10202,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>411</v>
       </c>
@@ -10302,7 +10320,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>417</v>
       </c>
@@ -10420,7 +10438,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>424</v>
       </c>
@@ -10538,7 +10556,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>430</v>
       </c>
@@ -10656,7 +10674,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>431</v>
       </c>
@@ -10776,7 +10794,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>432</v>
       </c>
@@ -10898,7 +10916,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>437</v>
       </c>
@@ -11016,7 +11034,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>444</v>
       </c>
@@ -11134,7 +11152,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>449</v>
       </c>
@@ -11252,7 +11270,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
         <v>455</v>
       </c>
@@ -11372,7 +11390,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>461</v>
       </c>
@@ -11490,7 +11508,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>462</v>
       </c>
@@ -11610,7 +11628,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>463</v>
       </c>
@@ -11732,7 +11750,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
         <v>464</v>
       </c>
@@ -11850,7 +11868,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>473</v>
       </c>
@@ -11968,7 +11986,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
         <v>477</v>
       </c>
@@ -12087,6 +12105,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP85">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI84">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -9,9 +9,6 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-25T17:34:53+00:00</t>
+    <t>2023-04-30T20:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-condition</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Condition</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -1654,21 +1651,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2016,7 +1998,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2134,7 +2116,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2254,7 +2236,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -2372,7 +2354,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>103</v>
       </c>
@@ -2492,7 +2474,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>109</v>
       </c>
@@ -2612,7 +2594,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -2732,7 +2714,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -2852,7 +2834,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>134</v>
       </c>
@@ -2968,7 +2950,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
@@ -3090,7 +3072,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3210,7 +3192,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>155</v>
       </c>
@@ -3330,7 +3312,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>160</v>
       </c>
@@ -3452,7 +3434,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>167</v>
       </c>
@@ -3574,7 +3556,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>176</v>
       </c>
@@ -3593,7 +3575,7 @@
         <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>91</v>
@@ -3694,7 +3676,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>190</v>
       </c>
@@ -3713,7 +3695,7 @@
         <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>91</v>
@@ -3814,7 +3796,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>201</v>
       </c>
@@ -3833,7 +3815,7 @@
         <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
@@ -3934,7 +3916,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>211</v>
       </c>
@@ -4054,7 +4036,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>221</v>
       </c>
@@ -4067,13 +4049,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>79</v>
@@ -4174,7 +4156,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>235</v>
       </c>
@@ -4292,7 +4274,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>241</v>
       </c>
@@ -4412,7 +4394,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>246</v>
       </c>
@@ -4534,7 +4516,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>257</v>
       </c>
@@ -4658,7 +4640,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>260</v>
       </c>
@@ -4776,7 +4758,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>262</v>
       </c>
@@ -4896,7 +4878,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>264</v>
       </c>
@@ -5018,7 +5000,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>274</v>
       </c>
@@ -5138,7 +5120,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>282</v>
       </c>
@@ -5258,7 +5240,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>290</v>
       </c>
@@ -5378,7 +5360,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>298</v>
       </c>
@@ -5500,7 +5482,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>308</v>
       </c>
@@ -5622,7 +5604,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>311</v>
       </c>
@@ -5740,7 +5722,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>312</v>
       </c>
@@ -5860,7 +5842,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>313</v>
       </c>
@@ -5982,7 +5964,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>315</v>
       </c>
@@ -6102,7 +6084,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>316</v>
       </c>
@@ -6222,7 +6204,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>317</v>
       </c>
@@ -6342,7 +6324,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>318</v>
       </c>
@@ -6464,7 +6446,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>319</v>
       </c>
@@ -6588,7 +6570,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>322</v>
       </c>
@@ -6706,7 +6688,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>323</v>
       </c>
@@ -6826,7 +6808,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>324</v>
       </c>
@@ -6948,7 +6930,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>326</v>
       </c>
@@ -7068,7 +7050,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>327</v>
       </c>
@@ -7188,7 +7170,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>328</v>
       </c>
@@ -7308,7 +7290,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>329</v>
       </c>
@@ -7430,7 +7412,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>330</v>
       </c>
@@ -7554,7 +7536,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>333</v>
       </c>
@@ -7672,7 +7654,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>334</v>
       </c>
@@ -7792,7 +7774,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>335</v>
       </c>
@@ -7914,7 +7896,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>337</v>
       </c>
@@ -8034,7 +8016,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>338</v>
       </c>
@@ -8154,7 +8136,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>339</v>
       </c>
@@ -8274,7 +8256,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>340</v>
       </c>
@@ -8396,7 +8378,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>341</v>
       </c>
@@ -8520,7 +8502,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>344</v>
       </c>
@@ -8638,7 +8620,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>345</v>
       </c>
@@ -8758,7 +8740,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>346</v>
       </c>
@@ -8880,7 +8862,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>348</v>
       </c>
@@ -9000,7 +8982,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>349</v>
       </c>
@@ -9120,7 +9102,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>350</v>
       </c>
@@ -9240,7 +9222,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>351</v>
       </c>
@@ -9362,7 +9344,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>352</v>
       </c>
@@ -9484,7 +9466,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>360</v>
       </c>
@@ -9604,7 +9586,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>369</v>
       </c>
@@ -9623,7 +9605,7 @@
         <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>79</v>
@@ -9724,7 +9706,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>379</v>
       </c>
@@ -9844,7 +9826,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>388</v>
       </c>
@@ -9964,7 +9946,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>397</v>
       </c>
@@ -10084,7 +10066,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>404</v>
       </c>
@@ -10202,7 +10184,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>411</v>
       </c>
@@ -10320,7 +10302,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>417</v>
       </c>
@@ -10438,7 +10420,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>424</v>
       </c>
@@ -10556,7 +10538,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>430</v>
       </c>
@@ -10674,7 +10656,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>431</v>
       </c>
@@ -10794,7 +10776,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>432</v>
       </c>
@@ -10916,7 +10898,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>437</v>
       </c>
@@ -11034,7 +11016,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>444</v>
       </c>
@@ -11152,7 +11134,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>449</v>
       </c>
@@ -11270,7 +11252,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
         <v>455</v>
       </c>
@@ -11390,7 +11372,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>461</v>
       </c>
@@ -11508,7 +11490,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>462</v>
       </c>
@@ -11628,7 +11610,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>463</v>
       </c>
@@ -11750,7 +11732,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>464</v>
       </c>
@@ -11868,7 +11850,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>473</v>
       </c>
@@ -11986,7 +11968,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
         <v>477</v>
       </c>
@@ -12105,24 +12087,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP85">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T20:59:20+00:00</t>
+    <t>2023-04-30T21:23:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T21:23:00+00:00</t>
+    <t>2023-05-05T00:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3275" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3275" uniqueCount="485">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>3.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T00:02:52+00:00</t>
+    <t>2023-11-28T12:13:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,6 +269,10 @@
   </si>
   <si>
     <t>A clinical condition, problem, diagnosis, or other event, situation, issue, or clinical concept that has risen to a level of concern.</t>
+  </si>
+  <si>
+    <t>con-3:Condition.clinicalStatus SHALL be present if verificationStatus is not entered-in-error and category is problem-list-item {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
+con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1644,10 +1648,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -2095,19 +2099,19 @@
         <v>79</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>79</v>
@@ -2118,10 +2122,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2132,7 +2136,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>79</v>
@@ -2141,19 +2145,19 @@
         <v>79</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2203,13 +2207,13 @@
         <v>79</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>79</v>
@@ -2238,10 +2242,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2252,7 +2256,7 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>79</v>
@@ -2261,16 +2265,16 @@
         <v>79</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2321,19 +2325,19 @@
         <v>79</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>79</v>
@@ -2356,10 +2360,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2370,28 +2374,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2441,19 +2445,19 @@
         <v>79</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>79</v>
@@ -2476,10 +2480,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2490,7 +2494,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>79</v>
@@ -2502,16 +2506,16 @@
         <v>79</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2537,13 +2541,13 @@
         <v>79</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>79</v>
@@ -2561,19 +2565,19 @@
         <v>79</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>79</v>
@@ -2596,21 +2600,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>79</v>
@@ -2622,16 +2626,16 @@
         <v>79</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2681,19 +2685,19 @@
         <v>79</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>79</v>
@@ -2705,7 +2709,7 @@
         <v>79</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>79</v>
@@ -2716,14 +2720,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2742,16 +2746,16 @@
         <v>79</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2801,7 +2805,7 @@
         <v>79</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2825,7 +2829,7 @@
         <v>79</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>79</v>
@@ -2836,10 +2840,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2862,13 +2866,13 @@
         <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2907,17 +2911,17 @@
         <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2929,7 +2933,7 @@
         <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>79</v>
@@ -2952,13 +2956,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>79</v>
@@ -2968,7 +2972,7 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>79</v>
@@ -2980,16 +2984,16 @@
         <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3039,7 +3043,7 @@
         <v>79</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3048,10 +3052,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>79</v>
@@ -3063,7 +3067,7 @@
         <v>79</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>79</v>
@@ -3074,13 +3078,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>79</v>
@@ -3090,7 +3094,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
@@ -3102,13 +3106,13 @@
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3159,7 +3163,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3168,10 +3172,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>79</v>
@@ -3194,13 +3198,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>79</v>
@@ -3210,7 +3214,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>79</v>
@@ -3222,13 +3226,13 @@
         <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3279,7 +3283,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3288,10 +3292,10 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>79</v>
@@ -3314,14 +3318,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3334,25 +3338,25 @@
         <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>79</v>
@@ -3401,7 +3405,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3413,7 +3417,7 @@
         <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>79</v>
@@ -3425,7 +3429,7 @@
         <v>79</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3436,10 +3440,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3459,22 +3463,22 @@
         <v>79</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3523,7 +3527,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3535,10 +3539,10 @@
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>79</v>
@@ -3547,10 +3551,10 @@
         <v>79</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>79</v>
@@ -3558,10 +3562,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3572,28 +3576,28 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3619,13 +3623,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -3643,34 +3647,34 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>79</v>
@@ -3678,10 +3682,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3692,28 +3696,28 @@
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3739,13 +3743,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3763,45 +3767,45 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AG16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>189</v>
-      </c>
       <c r="AP16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3824,16 +3828,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3859,13 +3863,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3883,7 +3887,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3895,22 +3899,22 @@
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -3918,10 +3922,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3932,7 +3936,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>79</v>
@@ -3944,16 +3948,16 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3979,13 +3983,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -4003,56 +4007,56 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -4061,20 +4065,20 @@
         <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4099,13 +4103,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -4123,45 +4127,45 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4172,7 +4176,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>79</v>
@@ -4184,13 +4188,13 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4241,13 +4245,13 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
@@ -4265,7 +4269,7 @@
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4276,14 +4280,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4302,16 +4306,16 @@
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4349,19 +4353,19 @@
         <v>79</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4373,7 +4377,7 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
@@ -4385,7 +4389,7 @@
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4396,10 +4400,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4419,22 +4423,22 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4471,19 +4475,19 @@
         <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4495,7 +4499,7 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
@@ -4504,10 +4508,10 @@
         <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4518,13 +4522,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>79</v>
@@ -4534,7 +4538,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>79</v>
@@ -4543,22 +4547,22 @@
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -4607,7 +4611,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4619,7 +4623,7 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
@@ -4628,10 +4632,10 @@
         <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4642,10 +4646,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4656,7 +4660,7 @@
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>79</v>
@@ -4668,13 +4672,13 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4725,13 +4729,13 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>79</v>
@@ -4749,7 +4753,7 @@
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4760,14 +4764,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4786,16 +4790,16 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4833,19 +4837,19 @@
         <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4857,7 +4861,7 @@
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
@@ -4869,7 +4873,7 @@
         <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -4880,10 +4884,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4891,10 +4895,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -4903,22 +4907,22 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -4928,7 +4932,7 @@
         <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>79</v>
@@ -4967,19 +4971,19 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
@@ -4988,10 +4992,10 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -5002,10 +5006,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5016,7 +5020,7 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -5025,19 +5029,19 @@
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5087,19 +5091,19 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>79</v>
@@ -5108,10 +5112,10 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5122,10 +5126,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5136,7 +5140,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
@@ -5145,20 +5149,20 @@
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5207,19 +5211,19 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>79</v>
@@ -5228,10 +5232,10 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5242,10 +5246,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5256,7 +5260,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>79</v>
@@ -5265,20 +5269,20 @@
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5327,19 +5331,19 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>79</v>
@@ -5348,10 +5352,10 @@
         <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5362,10 +5366,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5376,7 +5380,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5385,22 +5389,22 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5449,19 +5453,19 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>79</v>
@@ -5470,10 +5474,10 @@
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5484,13 +5488,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
@@ -5500,7 +5504,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5509,22 +5513,22 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5549,11 +5553,11 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5571,7 +5575,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5583,7 +5587,7 @@
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
@@ -5592,10 +5596,10 @@
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5606,10 +5610,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5620,7 +5624,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
@@ -5632,13 +5636,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5689,13 +5693,13 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
@@ -5713,7 +5717,7 @@
         <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5724,14 +5728,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5750,16 +5754,16 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5797,19 +5801,19 @@
         <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5821,7 +5825,7 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
@@ -5833,7 +5837,7 @@
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5844,10 +5848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5855,10 +5859,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
@@ -5867,22 +5871,22 @@
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5892,7 +5896,7 @@
         <v>79</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>79</v>
@@ -5931,19 +5935,19 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
@@ -5952,10 +5956,10 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5966,10 +5970,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5980,7 +5984,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
@@ -5989,19 +5993,19 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6051,19 +6055,19 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
@@ -6072,10 +6076,10 @@
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
@@ -6086,10 +6090,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6100,7 +6104,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>79</v>
@@ -6109,20 +6113,20 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6171,19 +6175,19 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>79</v>
@@ -6192,10 +6196,10 @@
         <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6206,10 +6210,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6220,7 +6224,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -6229,20 +6233,20 @@
         <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6291,19 +6295,19 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>79</v>
@@ -6312,10 +6316,10 @@
         <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6326,10 +6330,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6340,7 +6344,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -6349,22 +6353,22 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6413,19 +6417,19 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>79</v>
@@ -6434,10 +6438,10 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6448,13 +6452,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -6464,7 +6468,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6473,22 +6477,22 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6537,7 +6541,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6549,7 +6553,7 @@
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
@@ -6558,10 +6562,10 @@
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6572,10 +6576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6586,7 +6590,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -6598,13 +6602,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6655,13 +6659,13 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
@@ -6679,7 +6683,7 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6690,14 +6694,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6716,16 +6720,16 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6763,19 +6767,19 @@
         <v>79</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6787,7 +6791,7 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
@@ -6799,7 +6803,7 @@
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6810,10 +6814,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6821,10 +6825,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -6833,22 +6837,22 @@
         <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6858,7 +6862,7 @@
         <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>79</v>
@@ -6897,19 +6901,19 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -6918,10 +6922,10 @@
         <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6932,10 +6936,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6946,7 +6950,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
@@ -6955,19 +6959,19 @@
         <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7017,19 +7021,19 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
@@ -7038,10 +7042,10 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7052,10 +7056,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7066,7 +7070,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -7075,20 +7079,20 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7137,19 +7141,19 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
@@ -7158,10 +7162,10 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7172,10 +7176,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7186,7 +7190,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7195,20 +7199,20 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7257,19 +7261,19 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
@@ -7278,10 +7282,10 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7292,10 +7296,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7306,7 +7310,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7315,22 +7319,22 @@
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7379,19 +7383,19 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
@@ -7400,10 +7404,10 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7414,13 +7418,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>79</v>
@@ -7430,7 +7434,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7439,22 +7443,22 @@
         <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7503,7 +7507,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7515,7 +7519,7 @@
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
@@ -7524,10 +7528,10 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7538,10 +7542,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7552,7 +7556,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>79</v>
@@ -7564,13 +7568,13 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7621,13 +7625,13 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
@@ -7645,7 +7649,7 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7656,14 +7660,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7682,16 +7686,16 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7729,19 +7733,19 @@
         <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7753,7 +7757,7 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
@@ -7765,7 +7769,7 @@
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7776,10 +7780,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7787,10 +7791,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7799,22 +7803,22 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7824,7 +7828,7 @@
         <v>79</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>79</v>
@@ -7863,19 +7867,19 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
@@ -7884,10 +7888,10 @@
         <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7898,10 +7902,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7912,7 +7916,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
@@ -7921,19 +7925,19 @@
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7983,19 +7987,19 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
@@ -8004,10 +8008,10 @@
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8018,10 +8022,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8032,7 +8036,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -8041,20 +8045,20 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8103,19 +8107,19 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8124,10 +8128,10 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8138,10 +8142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8152,7 +8156,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8161,20 +8165,20 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8223,19 +8227,19 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
@@ -8244,10 +8248,10 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8258,10 +8262,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8272,7 +8276,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -8281,22 +8285,22 @@
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8345,19 +8349,19 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
@@ -8366,10 +8370,10 @@
         <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8380,13 +8384,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>79</v>
@@ -8396,7 +8400,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -8405,22 +8409,22 @@
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8469,7 +8473,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8481,7 +8485,7 @@
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
@@ -8490,10 +8494,10 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8504,10 +8508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8518,7 +8522,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8530,13 +8534,13 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8587,13 +8591,13 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -8611,7 +8615,7 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8622,14 +8626,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8648,16 +8652,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8695,19 +8699,19 @@
         <v>79</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8719,7 +8723,7 @@
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
@@ -8731,7 +8735,7 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8742,10 +8746,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8753,10 +8757,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8765,22 +8769,22 @@
         <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -8790,7 +8794,7 @@
         <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>79</v>
@@ -8829,19 +8833,19 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
@@ -8850,10 +8854,10 @@
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8864,10 +8868,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8878,7 +8882,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -8887,19 +8891,19 @@
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8949,19 +8953,19 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
@@ -8970,10 +8974,10 @@
         <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -8984,10 +8988,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8998,7 +9002,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -9007,20 +9011,20 @@
         <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9069,19 +9073,19 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>79</v>
@@ -9090,10 +9094,10 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9104,10 +9108,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9118,7 +9122,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -9127,20 +9131,20 @@
         <v>79</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9189,19 +9193,19 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>79</v>
@@ -9210,10 +9214,10 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9224,10 +9228,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9238,7 +9242,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>79</v>
@@ -9247,22 +9251,22 @@
         <v>79</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -9311,19 +9315,19 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
@@ -9332,10 +9336,10 @@
         <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9346,10 +9350,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9360,7 +9364,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
@@ -9369,22 +9373,22 @@
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -9433,19 +9437,19 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
@@ -9454,10 +9458,10 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9468,10 +9472,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9491,19 +9495,19 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9529,13 +9533,13 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9553,7 +9557,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9565,44 +9569,44 @@
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
@@ -9611,20 +9615,20 @@
         <v>79</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9673,34 +9677,34 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
@@ -9708,10 +9712,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9722,7 +9726,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>79</v>
@@ -9731,19 +9735,19 @@
         <v>79</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9793,34 +9797,34 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>79</v>
@@ -9828,10 +9832,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9842,7 +9846,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>79</v>
@@ -9851,19 +9855,19 @@
         <v>79</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9913,34 +9917,34 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -9948,10 +9952,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9962,7 +9966,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>79</v>
@@ -9974,16 +9978,16 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10033,19 +10037,19 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
@@ -10057,10 +10061,10 @@
         <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>79</v>
@@ -10068,10 +10072,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10082,7 +10086,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>
@@ -10091,16 +10095,16 @@
         <v>79</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10151,19 +10155,19 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
@@ -10172,13 +10176,13 @@
         <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>79</v>
@@ -10186,10 +10190,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10200,7 +10204,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -10209,16 +10213,16 @@
         <v>79</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10269,19 +10273,19 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
@@ -10293,10 +10297,10 @@
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>79</v>
@@ -10304,10 +10308,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10318,7 +10322,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>79</v>
@@ -10327,16 +10331,16 @@
         <v>79</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10387,19 +10391,19 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
@@ -10408,13 +10412,13 @@
         <v>79</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>79</v>
@@ -10422,10 +10426,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10448,13 +10452,13 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10505,7 +10509,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10517,7 +10521,7 @@
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
@@ -10529,7 +10533,7 @@
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10540,10 +10544,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10554,7 +10558,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -10566,13 +10570,13 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10623,13 +10627,13 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>79</v>
@@ -10647,7 +10651,7 @@
         <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10658,14 +10662,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10684,16 +10688,16 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10743,7 +10747,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10755,7 +10759,7 @@
         <v>79</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
@@ -10767,7 +10771,7 @@
         <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -10778,14 +10782,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10798,25 +10802,25 @@
         <v>79</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -10865,7 +10869,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10877,7 +10881,7 @@
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
@@ -10889,7 +10893,7 @@
         <v>79</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -10900,10 +10904,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10914,7 +10918,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>79</v>
@@ -10926,13 +10930,13 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10959,13 +10963,13 @@
         <v>79</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>79</v>
@@ -10983,31 +10987,31 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>79</v>
@@ -11018,10 +11022,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11044,13 +11048,13 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11101,7 +11105,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11110,10 +11114,10 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
@@ -11125,7 +11129,7 @@
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>79</v>
@@ -11136,10 +11140,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11150,7 +11154,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>79</v>
@@ -11162,13 +11166,13 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11195,13 +11199,13 @@
         <v>79</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>79</v>
@@ -11219,19 +11223,19 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
@@ -11243,7 +11247,7 @@
         <v>79</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -11254,10 +11258,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11280,16 +11284,16 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11339,7 +11343,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11351,7 +11355,7 @@
         <v>79</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>79</v>
@@ -11363,7 +11367,7 @@
         <v>79</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -11374,10 +11378,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11388,7 +11392,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>79</v>
@@ -11400,13 +11404,13 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11457,13 +11461,13 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>79</v>
@@ -11481,7 +11485,7 @@
         <v>79</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -11492,14 +11496,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11518,16 +11522,16 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11577,7 +11581,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11589,7 +11593,7 @@
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
@@ -11601,7 +11605,7 @@
         <v>79</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -11612,14 +11616,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11632,25 +11636,25 @@
         <v>79</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -11699,7 +11703,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11711,7 +11715,7 @@
         <v>79</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>79</v>
@@ -11723,7 +11727,7 @@
         <v>79</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -11734,10 +11738,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11757,16 +11761,16 @@
         <v>79</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11793,13 +11797,13 @@
         <v>79</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>79</v>
@@ -11817,7 +11821,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -11826,25 +11830,25 @@
         <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>79</v>
@@ -11852,10 +11856,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11875,16 +11879,16 @@
         <v>79</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11935,7 +11939,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -11944,10 +11948,10 @@
         <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>79</v>
@@ -11959,10 +11963,10 @@
         <v>79</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>
@@ -11970,10 +11974,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11996,13 +12000,13 @@
         <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12053,7 +12057,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12065,19 +12069,19 @@
         <v>79</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>79</v>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:13:03+00:00</t>
+    <t>2023-11-30T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T13:40:49+00:00</t>
+    <t>2023-11-30T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T14:55:40+00:00</t>
+    <t>2023-12-01T12:31:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T12:31:40+00:00</t>
+    <t>2023-12-01T13:42:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T13:42:49+00:00</t>
+    <t>2023-12-19T10:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1301,7 +1301,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1841,7 +1841,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="150.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="196.45703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1301,7 +1301,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1841,7 +1841,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="196.45703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="150.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -1301,7 +1301,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1841,7 +1841,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="150.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="196.45703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -477,27 +477,27 @@
     <t>Although a condition may be caused by a substance, this is not intended to be used to record allergies/adverse reactions to substances.</t>
   </si>
   <si>
+    <t>.typeCode</t>
+  </si>
+  <si>
+    <t>Condition.extension:conditionLastAssertedDate</t>
+  </si>
+  <si>
+    <t>conditionLastAssertedDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.dk/fhir/core/StructureDefinition/ConditionLastAssertedDate}
+</t>
+  </si>
+  <si>
+    <t>Last date a condition was confirmed valid in its current state</t>
+  </si>
+  <si>
+    <t>Extension for the last date a Condition-instance was confirmed valid in its current state. E.g. with its current clinical- and verification status, stage and severity. Typically the last performed follow-up</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>.typeCode</t>
-  </si>
-  <si>
-    <t>Condition.extension:conditionLastAssertedDate</t>
-  </si>
-  <si>
-    <t>conditionLastAssertedDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.dk/fhir/core/StructureDefinition/ConditionLastAssertedDate}
-</t>
-  </si>
-  <si>
-    <t>Last date a condition was confirmed valid in its current state</t>
-  </si>
-  <si>
-    <t>Extension for the last date a Condition-instance was confirmed valid in its current state. E.g. with its current clinical- and verification status, stage and severity. Typically the last performed follow-up</t>
   </si>
   <si>
     <t>Condition.extension:notFollowedAnymore</t>
@@ -3052,7 +3052,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -3067,7 +3067,7 @@
         <v>79</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>79</v>
@@ -3078,13 +3078,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>79</v>
@@ -3106,13 +3106,13 @@
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3172,7 +3172,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>142</v>
@@ -3292,7 +3292,7 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>142</v>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1301,7 +1301,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1320,7 +1320,7 @@
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role)
 </t>
   </si>
   <si>
@@ -1841,7 +1841,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="196.45703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="242.4765625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Condition</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-condition</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -1301,7 +1304,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1320,7 +1323,7 @@
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole)
 </t>
   </si>
   <si>
@@ -1655,6 +1658,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1841,7 +1859,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="242.4765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="196.45703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2002,7 +2020,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2120,7 +2138,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>90</v>
       </c>
@@ -2240,7 +2258,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>98</v>
       </c>
@@ -2358,7 +2376,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>104</v>
       </c>
@@ -2478,7 +2496,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>110</v>
       </c>
@@ -2598,7 +2616,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>119</v>
       </c>
@@ -2718,7 +2736,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>127</v>
       </c>
@@ -2838,7 +2856,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>135</v>
       </c>
@@ -2954,7 +2972,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>143</v>
       </c>
@@ -3076,7 +3094,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3196,7 +3214,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
@@ -3316,7 +3334,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -3438,7 +3456,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
@@ -3560,7 +3578,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>177</v>
       </c>
@@ -3579,7 +3597,7 @@
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>92</v>
@@ -3680,7 +3698,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>191</v>
       </c>
@@ -3699,7 +3717,7 @@
         <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>92</v>
@@ -3800,7 +3818,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>202</v>
       </c>
@@ -3819,7 +3837,7 @@
         <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
@@ -3920,7 +3938,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>212</v>
       </c>
@@ -4040,7 +4058,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>222</v>
       </c>
@@ -4053,13 +4071,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>79</v>
@@ -4160,7 +4178,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>236</v>
       </c>
@@ -4278,7 +4296,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>242</v>
       </c>
@@ -4398,7 +4416,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>247</v>
       </c>
@@ -4520,7 +4538,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>258</v>
       </c>
@@ -4644,7 +4662,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>261</v>
       </c>
@@ -4762,7 +4780,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>263</v>
       </c>
@@ -4882,7 +4900,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>265</v>
       </c>
@@ -5004,7 +5022,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>275</v>
       </c>
@@ -5124,7 +5142,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>283</v>
       </c>
@@ -5244,7 +5262,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>291</v>
       </c>
@@ -5364,7 +5382,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>299</v>
       </c>
@@ -5486,7 +5504,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>309</v>
       </c>
@@ -5608,7 +5626,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>312</v>
       </c>
@@ -5726,7 +5744,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>313</v>
       </c>
@@ -5846,7 +5864,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>314</v>
       </c>
@@ -5968,7 +5986,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>316</v>
       </c>
@@ -6088,7 +6106,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>317</v>
       </c>
@@ -6208,7 +6226,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>318</v>
       </c>
@@ -6328,7 +6346,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>319</v>
       </c>
@@ -6450,7 +6468,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>320</v>
       </c>
@@ -6574,7 +6592,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>323</v>
       </c>
@@ -6692,7 +6710,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>324</v>
       </c>
@@ -6812,7 +6830,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>325</v>
       </c>
@@ -6934,7 +6952,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>327</v>
       </c>
@@ -7054,7 +7072,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>328</v>
       </c>
@@ -7174,7 +7192,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>329</v>
       </c>
@@ -7294,7 +7312,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>330</v>
       </c>
@@ -7416,7 +7434,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>331</v>
       </c>
@@ -7540,7 +7558,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>334</v>
       </c>
@@ -7658,7 +7676,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>335</v>
       </c>
@@ -7778,7 +7796,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>336</v>
       </c>
@@ -7900,7 +7918,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>338</v>
       </c>
@@ -8020,7 +8038,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>339</v>
       </c>
@@ -8140,7 +8158,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>340</v>
       </c>
@@ -8260,7 +8278,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>341</v>
       </c>
@@ -8382,7 +8400,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>342</v>
       </c>
@@ -8506,7 +8524,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>345</v>
       </c>
@@ -8624,7 +8642,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>346</v>
       </c>
@@ -8744,7 +8762,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>347</v>
       </c>
@@ -8866,7 +8884,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>349</v>
       </c>
@@ -8986,7 +9004,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>350</v>
       </c>
@@ -9106,7 +9124,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>351</v>
       </c>
@@ -9226,7 +9244,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>352</v>
       </c>
@@ -9348,7 +9366,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>353</v>
       </c>
@@ -9470,7 +9488,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>361</v>
       </c>
@@ -9590,7 +9608,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>370</v>
       </c>
@@ -9609,7 +9627,7 @@
         <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>79</v>
@@ -9710,7 +9728,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>380</v>
       </c>
@@ -9830,7 +9848,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>389</v>
       </c>
@@ -9950,7 +9968,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>398</v>
       </c>
@@ -10070,7 +10088,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>405</v>
       </c>
@@ -10188,7 +10206,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>412</v>
       </c>
@@ -10306,7 +10324,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>418</v>
       </c>
@@ -10424,7 +10442,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>425</v>
       </c>
@@ -10542,7 +10560,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>431</v>
       </c>
@@ -10660,7 +10678,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>432</v>
       </c>
@@ -10780,7 +10798,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>433</v>
       </c>
@@ -10902,7 +10920,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>438</v>
       </c>
@@ -11020,7 +11038,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>445</v>
       </c>
@@ -11138,7 +11156,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>450</v>
       </c>
@@ -11256,7 +11274,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
         <v>456</v>
       </c>
@@ -11376,7 +11394,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>462</v>
       </c>
@@ -11494,7 +11512,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>463</v>
       </c>
@@ -11614,7 +11632,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>464</v>
       </c>
@@ -11736,7 +11754,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
         <v>465</v>
       </c>
@@ -11854,7 +11872,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>474</v>
       </c>
@@ -11972,7 +11990,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
         <v>478</v>
       </c>
@@ -12091,6 +12109,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP85">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI84">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1304,7 +1304,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1323,7 +1323,7 @@
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role)
 </t>
   </si>
   <si>
@@ -1859,7 +1859,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="196.45703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="242.4765625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -9,9 +9,6 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-condition</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Condition</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -1304,7 +1301,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1323,7 +1320,7 @@
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole)
 </t>
   </si>
   <si>
@@ -1658,21 +1655,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1859,7 +1841,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="242.4765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="196.45703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2020,7 +2002,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2138,7 +2120,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>90</v>
       </c>
@@ -2258,7 +2240,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>98</v>
       </c>
@@ -2376,7 +2358,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>104</v>
       </c>
@@ -2496,7 +2478,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>110</v>
       </c>
@@ -2616,7 +2598,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>119</v>
       </c>
@@ -2736,7 +2718,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>127</v>
       </c>
@@ -2856,7 +2838,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>135</v>
       </c>
@@ -2972,7 +2954,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>143</v>
       </c>
@@ -3094,7 +3076,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3214,7 +3196,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
@@ -3334,7 +3316,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -3456,7 +3438,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
@@ -3578,7 +3560,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>177</v>
       </c>
@@ -3597,7 +3579,7 @@
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>92</v>
@@ -3698,7 +3680,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>191</v>
       </c>
@@ -3717,7 +3699,7 @@
         <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>92</v>
@@ -3818,7 +3800,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>202</v>
       </c>
@@ -3837,7 +3819,7 @@
         <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
@@ -3938,7 +3920,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>212</v>
       </c>
@@ -4058,7 +4040,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>222</v>
       </c>
@@ -4071,13 +4053,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>79</v>
@@ -4178,7 +4160,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>236</v>
       </c>
@@ -4296,7 +4278,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>242</v>
       </c>
@@ -4416,7 +4398,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>247</v>
       </c>
@@ -4538,7 +4520,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>258</v>
       </c>
@@ -4662,7 +4644,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>261</v>
       </c>
@@ -4780,7 +4762,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>263</v>
       </c>
@@ -4900,7 +4882,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>265</v>
       </c>
@@ -5022,7 +5004,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>275</v>
       </c>
@@ -5142,7 +5124,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>283</v>
       </c>
@@ -5262,7 +5244,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>291</v>
       </c>
@@ -5382,7 +5364,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>299</v>
       </c>
@@ -5504,7 +5486,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>309</v>
       </c>
@@ -5626,7 +5608,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>312</v>
       </c>
@@ -5744,7 +5726,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>313</v>
       </c>
@@ -5864,7 +5846,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>314</v>
       </c>
@@ -5986,7 +5968,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>316</v>
       </c>
@@ -6106,7 +6088,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>317</v>
       </c>
@@ -6226,7 +6208,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>318</v>
       </c>
@@ -6346,7 +6328,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>319</v>
       </c>
@@ -6468,7 +6450,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>320</v>
       </c>
@@ -6592,7 +6574,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>323</v>
       </c>
@@ -6710,7 +6692,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>324</v>
       </c>
@@ -6830,7 +6812,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>325</v>
       </c>
@@ -6952,7 +6934,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>327</v>
       </c>
@@ -7072,7 +7054,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>328</v>
       </c>
@@ -7192,7 +7174,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>329</v>
       </c>
@@ -7312,7 +7294,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>330</v>
       </c>
@@ -7434,7 +7416,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>331</v>
       </c>
@@ -7558,7 +7540,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>334</v>
       </c>
@@ -7676,7 +7658,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>335</v>
       </c>
@@ -7796,7 +7778,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>336</v>
       </c>
@@ -7918,7 +7900,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>338</v>
       </c>
@@ -8038,7 +8020,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>339</v>
       </c>
@@ -8158,7 +8140,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>340</v>
       </c>
@@ -8278,7 +8260,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>341</v>
       </c>
@@ -8400,7 +8382,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>342</v>
       </c>
@@ -8524,7 +8506,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>345</v>
       </c>
@@ -8642,7 +8624,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>346</v>
       </c>
@@ -8762,7 +8744,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>347</v>
       </c>
@@ -8884,7 +8866,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>349</v>
       </c>
@@ -9004,7 +8986,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>350</v>
       </c>
@@ -9124,7 +9106,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>351</v>
       </c>
@@ -9244,7 +9226,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>352</v>
       </c>
@@ -9366,7 +9348,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>353</v>
       </c>
@@ -9488,7 +9470,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>361</v>
       </c>
@@ -9608,7 +9590,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>370</v>
       </c>
@@ -9627,7 +9609,7 @@
         <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>79</v>
@@ -9728,7 +9710,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>380</v>
       </c>
@@ -9848,7 +9830,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>389</v>
       </c>
@@ -9968,7 +9950,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>398</v>
       </c>
@@ -10088,7 +10070,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>405</v>
       </c>
@@ -10206,7 +10188,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>412</v>
       </c>
@@ -10324,7 +10306,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>418</v>
       </c>
@@ -10442,7 +10424,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>425</v>
       </c>
@@ -10560,7 +10542,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>431</v>
       </c>
@@ -10678,7 +10660,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>432</v>
       </c>
@@ -10798,7 +10780,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>433</v>
       </c>
@@ -10920,7 +10902,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>438</v>
       </c>
@@ -11038,7 +11020,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>445</v>
       </c>
@@ -11156,7 +11138,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>450</v>
       </c>
@@ -11274,7 +11256,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
         <v>456</v>
       </c>
@@ -11394,7 +11376,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>462</v>
       </c>
@@ -11512,7 +11494,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>463</v>
       </c>
@@ -11632,7 +11614,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>464</v>
       </c>
@@ -11754,7 +11736,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>465</v>
       </c>
@@ -11872,7 +11854,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>474</v>
       </c>
@@ -11990,7 +11972,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
         <v>478</v>
       </c>
@@ -12109,24 +12091,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP85">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Condition</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-condition</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -1301,7 +1304,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1320,7 +1323,7 @@
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role)
 </t>
   </si>
   <si>
@@ -1655,6 +1658,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1841,7 +1859,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="196.45703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="242.4765625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2002,7 +2020,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2120,7 +2138,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>90</v>
       </c>
@@ -2240,7 +2258,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>98</v>
       </c>
@@ -2358,7 +2376,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>104</v>
       </c>
@@ -2478,7 +2496,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>110</v>
       </c>
@@ -2598,7 +2616,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>119</v>
       </c>
@@ -2718,7 +2736,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>127</v>
       </c>
@@ -2838,7 +2856,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>135</v>
       </c>
@@ -2954,7 +2972,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>143</v>
       </c>
@@ -3076,7 +3094,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3196,7 +3214,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
@@ -3316,7 +3334,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -3438,7 +3456,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
@@ -3560,7 +3578,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>177</v>
       </c>
@@ -3579,7 +3597,7 @@
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>92</v>
@@ -3680,7 +3698,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>191</v>
       </c>
@@ -3699,7 +3717,7 @@
         <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>92</v>
@@ -3800,7 +3818,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>202</v>
       </c>
@@ -3819,7 +3837,7 @@
         <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
@@ -3920,7 +3938,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>212</v>
       </c>
@@ -4040,7 +4058,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>222</v>
       </c>
@@ -4053,13 +4071,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>79</v>
@@ -4160,7 +4178,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>236</v>
       </c>
@@ -4278,7 +4296,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>242</v>
       </c>
@@ -4398,7 +4416,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>247</v>
       </c>
@@ -4520,7 +4538,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>258</v>
       </c>
@@ -4644,7 +4662,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>261</v>
       </c>
@@ -4762,7 +4780,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>263</v>
       </c>
@@ -4882,7 +4900,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>265</v>
       </c>
@@ -5004,7 +5022,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>275</v>
       </c>
@@ -5124,7 +5142,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>283</v>
       </c>
@@ -5244,7 +5262,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>291</v>
       </c>
@@ -5364,7 +5382,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>299</v>
       </c>
@@ -5486,7 +5504,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>309</v>
       </c>
@@ -5608,7 +5626,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>312</v>
       </c>
@@ -5726,7 +5744,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>313</v>
       </c>
@@ -5846,7 +5864,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>314</v>
       </c>
@@ -5968,7 +5986,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>316</v>
       </c>
@@ -6088,7 +6106,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>317</v>
       </c>
@@ -6208,7 +6226,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>318</v>
       </c>
@@ -6328,7 +6346,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>319</v>
       </c>
@@ -6450,7 +6468,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>320</v>
       </c>
@@ -6574,7 +6592,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>323</v>
       </c>
@@ -6692,7 +6710,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>324</v>
       </c>
@@ -6812,7 +6830,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>325</v>
       </c>
@@ -6934,7 +6952,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>327</v>
       </c>
@@ -7054,7 +7072,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>328</v>
       </c>
@@ -7174,7 +7192,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>329</v>
       </c>
@@ -7294,7 +7312,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>330</v>
       </c>
@@ -7416,7 +7434,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>331</v>
       </c>
@@ -7540,7 +7558,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>334</v>
       </c>
@@ -7658,7 +7676,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>335</v>
       </c>
@@ -7778,7 +7796,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>336</v>
       </c>
@@ -7900,7 +7918,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>338</v>
       </c>
@@ -8020,7 +8038,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>339</v>
       </c>
@@ -8140,7 +8158,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>340</v>
       </c>
@@ -8260,7 +8278,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>341</v>
       </c>
@@ -8382,7 +8400,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>342</v>
       </c>
@@ -8506,7 +8524,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>345</v>
       </c>
@@ -8624,7 +8642,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>346</v>
       </c>
@@ -8744,7 +8762,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>347</v>
       </c>
@@ -8866,7 +8884,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>349</v>
       </c>
@@ -8986,7 +9004,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>350</v>
       </c>
@@ -9106,7 +9124,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>351</v>
       </c>
@@ -9226,7 +9244,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>352</v>
       </c>
@@ -9348,7 +9366,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>353</v>
       </c>
@@ -9470,7 +9488,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>361</v>
       </c>
@@ -9590,7 +9608,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>370</v>
       </c>
@@ -9609,7 +9627,7 @@
         <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>79</v>
@@ -9710,7 +9728,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>380</v>
       </c>
@@ -9830,7 +9848,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>389</v>
       </c>
@@ -9950,7 +9968,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>398</v>
       </c>
@@ -10070,7 +10088,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>405</v>
       </c>
@@ -10188,7 +10206,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>412</v>
       </c>
@@ -10306,7 +10324,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>418</v>
       </c>
@@ -10424,7 +10442,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>425</v>
       </c>
@@ -10542,7 +10560,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>431</v>
       </c>
@@ -10660,7 +10678,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>432</v>
       </c>
@@ -10780,7 +10798,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>433</v>
       </c>
@@ -10902,7 +10920,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>438</v>
       </c>
@@ -11020,7 +11038,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>445</v>
       </c>
@@ -11138,7 +11156,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>450</v>
       </c>
@@ -11256,7 +11274,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
         <v>456</v>
       </c>
@@ -11376,7 +11394,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>462</v>
       </c>
@@ -11494,7 +11512,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>463</v>
       </c>
@@ -11614,7 +11632,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>464</v>
       </c>
@@ -11736,7 +11754,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
         <v>465</v>
       </c>
@@ -11854,7 +11872,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>474</v>
       </c>
@@ -11972,7 +11990,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
         <v>478</v>
       </c>
@@ -12091,6 +12109,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP85">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI84">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -9,9 +9,6 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-condition</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Condition</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -1304,7 +1301,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1323,7 +1320,7 @@
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole)
 </t>
   </si>
   <si>
@@ -1658,21 +1655,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1859,7 +1841,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="242.4765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="196.45703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2020,7 +2002,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2138,7 +2120,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>90</v>
       </c>
@@ -2258,7 +2240,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>98</v>
       </c>
@@ -2376,7 +2358,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>104</v>
       </c>
@@ -2496,7 +2478,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>110</v>
       </c>
@@ -2616,7 +2598,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>119</v>
       </c>
@@ -2736,7 +2718,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>127</v>
       </c>
@@ -2856,7 +2838,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>135</v>
       </c>
@@ -2972,7 +2954,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>143</v>
       </c>
@@ -3094,7 +3076,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3214,7 +3196,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
@@ -3334,7 +3316,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -3456,7 +3438,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
@@ -3578,7 +3560,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>177</v>
       </c>
@@ -3597,7 +3579,7 @@
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>92</v>
@@ -3698,7 +3680,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>191</v>
       </c>
@@ -3717,7 +3699,7 @@
         <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>92</v>
@@ -3818,7 +3800,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>202</v>
       </c>
@@ -3837,7 +3819,7 @@
         <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
@@ -3938,7 +3920,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>212</v>
       </c>
@@ -4058,7 +4040,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>222</v>
       </c>
@@ -4071,13 +4053,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>79</v>
@@ -4178,7 +4160,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>236</v>
       </c>
@@ -4296,7 +4278,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>242</v>
       </c>
@@ -4416,7 +4398,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>247</v>
       </c>
@@ -4538,7 +4520,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>258</v>
       </c>
@@ -4662,7 +4644,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>261</v>
       </c>
@@ -4780,7 +4762,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>263</v>
       </c>
@@ -4900,7 +4882,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>265</v>
       </c>
@@ -5022,7 +5004,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>275</v>
       </c>
@@ -5142,7 +5124,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>283</v>
       </c>
@@ -5262,7 +5244,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>291</v>
       </c>
@@ -5382,7 +5364,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>299</v>
       </c>
@@ -5504,7 +5486,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>309</v>
       </c>
@@ -5626,7 +5608,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>312</v>
       </c>
@@ -5744,7 +5726,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>313</v>
       </c>
@@ -5864,7 +5846,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>314</v>
       </c>
@@ -5986,7 +5968,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>316</v>
       </c>
@@ -6106,7 +6088,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>317</v>
       </c>
@@ -6226,7 +6208,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>318</v>
       </c>
@@ -6346,7 +6328,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>319</v>
       </c>
@@ -6468,7 +6450,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>320</v>
       </c>
@@ -6592,7 +6574,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>323</v>
       </c>
@@ -6710,7 +6692,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>324</v>
       </c>
@@ -6830,7 +6812,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>325</v>
       </c>
@@ -6952,7 +6934,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>327</v>
       </c>
@@ -7072,7 +7054,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>328</v>
       </c>
@@ -7192,7 +7174,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>329</v>
       </c>
@@ -7312,7 +7294,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>330</v>
       </c>
@@ -7434,7 +7416,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>331</v>
       </c>
@@ -7558,7 +7540,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>334</v>
       </c>
@@ -7676,7 +7658,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>335</v>
       </c>
@@ -7796,7 +7778,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>336</v>
       </c>
@@ -7918,7 +7900,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>338</v>
       </c>
@@ -8038,7 +8020,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>339</v>
       </c>
@@ -8158,7 +8140,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>340</v>
       </c>
@@ -8278,7 +8260,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>341</v>
       </c>
@@ -8400,7 +8382,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>342</v>
       </c>
@@ -8524,7 +8506,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>345</v>
       </c>
@@ -8642,7 +8624,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>346</v>
       </c>
@@ -8762,7 +8744,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>347</v>
       </c>
@@ -8884,7 +8866,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>349</v>
       </c>
@@ -9004,7 +8986,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>350</v>
       </c>
@@ -9124,7 +9106,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>351</v>
       </c>
@@ -9244,7 +9226,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>352</v>
       </c>
@@ -9366,7 +9348,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>353</v>
       </c>
@@ -9488,7 +9470,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>361</v>
       </c>
@@ -9608,7 +9590,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>370</v>
       </c>
@@ -9627,7 +9609,7 @@
         <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>79</v>
@@ -9728,7 +9710,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>380</v>
       </c>
@@ -9848,7 +9830,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>389</v>
       </c>
@@ -9968,7 +9950,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>398</v>
       </c>
@@ -10088,7 +10070,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>405</v>
       </c>
@@ -10206,7 +10188,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>412</v>
       </c>
@@ -10324,7 +10306,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>418</v>
       </c>
@@ -10442,7 +10424,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>425</v>
       </c>
@@ -10560,7 +10542,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>431</v>
       </c>
@@ -10678,7 +10660,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>432</v>
       </c>
@@ -10798,7 +10780,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>433</v>
       </c>
@@ -10920,7 +10902,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>438</v>
       </c>
@@ -11038,7 +11020,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>445</v>
       </c>
@@ -11156,7 +11138,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>450</v>
       </c>
@@ -11274,7 +11256,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
         <v>456</v>
       </c>
@@ -11394,7 +11376,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>462</v>
       </c>
@@ -11512,7 +11494,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>463</v>
       </c>
@@ -11632,7 +11614,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>464</v>
       </c>
@@ -11754,7 +11736,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>465</v>
       </c>
@@ -11872,7 +11854,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>474</v>
       </c>
@@ -11990,7 +11972,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
         <v>478</v>
       </c>
@@ -12109,24 +12091,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP85">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-condition.xlsx
+++ b/StructureDefinition-dk-core-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
